--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/OREGON_2016.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/OREGON_2016.xlsx
@@ -1860,7 +1860,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C84">
@@ -1939,7 +1939,7 @@
         <v>10</v>
       </c>
       <c r="D88">
-        <v>0.0009415309292910273</v>
+        <v>0.0009415309292910272</v>
       </c>
     </row>
     <row r="89">
@@ -2101,7 +2101,7 @@
         <v>10</v>
       </c>
       <c r="D97">
-        <v>0.0009415309292910273</v>
+        <v>0.0009415309292910272</v>
       </c>
     </row>
     <row r="98">
@@ -3379,7 +3379,7 @@
         <v>10</v>
       </c>
       <c r="D168">
-        <v>0.0009415309292910273</v>
+        <v>0.0009415309292910272</v>
       </c>
     </row>
     <row r="169">
@@ -3505,7 +3505,7 @@
         <v>10</v>
       </c>
       <c r="D175">
-        <v>0.0009415309292910273</v>
+        <v>0.0009415309292910272</v>
       </c>
     </row>
     <row r="176">
@@ -4243,7 +4243,7 @@
         <v>10</v>
       </c>
       <c r="D216">
-        <v>0.0009415309292910273</v>
+        <v>0.0009415309292910272</v>
       </c>
     </row>
     <row r="217">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C221">
@@ -4945,7 +4945,7 @@
         <v>10</v>
       </c>
       <c r="D255">
-        <v>0.0009415309292910273</v>
+        <v>0.0009415309292910272</v>
       </c>
     </row>
     <row r="256">
@@ -5179,7 +5179,7 @@
         <v>10</v>
       </c>
       <c r="D268">
-        <v>0.0009415309292910273</v>
+        <v>0.0009415309292910272</v>
       </c>
     </row>
     <row r="269">
@@ -5971,7 +5971,7 @@
         <v>10</v>
       </c>
       <c r="D312">
-        <v>0.0009415309292910273</v>
+        <v>0.0009415309292910272</v>
       </c>
     </row>
     <row r="313">
@@ -6097,7 +6097,7 @@
         <v>10</v>
       </c>
       <c r="D319">
-        <v>0.0009415309292910273</v>
+        <v>0.0009415309292910272</v>
       </c>
     </row>
     <row r="320">
@@ -6403,7 +6403,7 @@
         <v>10</v>
       </c>
       <c r="D336">
-        <v>0.0009415309292910273</v>
+        <v>0.0009415309292910272</v>
       </c>
     </row>
     <row r="337">
@@ -7771,7 +7771,7 @@
         <v>10</v>
       </c>
       <c r="D412">
-        <v>0.0009415309292910273</v>
+        <v>0.0009415309292910272</v>
       </c>
     </row>
     <row r="413">
@@ -8959,7 +8959,7 @@
         <v>10</v>
       </c>
       <c r="D478">
-        <v>0.0009415309292910273</v>
+        <v>0.0009415309292910272</v>
       </c>
     </row>
     <row r="479">
@@ -9661,7 +9661,7 @@
         <v>10</v>
       </c>
       <c r="D517">
-        <v>0.0009415309292910273</v>
+        <v>0.0009415309292910272</v>
       </c>
     </row>
     <row r="518">
@@ -9859,7 +9859,7 @@
         <v>10</v>
       </c>
       <c r="D528">
-        <v>0.0009415309292910273</v>
+        <v>0.0009415309292910272</v>
       </c>
     </row>
     <row r="529">
@@ -10705,7 +10705,7 @@
         <v>10</v>
       </c>
       <c r="D575">
-        <v>0.0009415309292910273</v>
+        <v>0.0009415309292910272</v>
       </c>
     </row>
     <row r="576">
@@ -11263,7 +11263,7 @@
         <v>10</v>
       </c>
       <c r="D606">
-        <v>0.0009415309292910273</v>
+        <v>0.0009415309292910272</v>
       </c>
     </row>
     <row r="607">
@@ -11623,7 +11623,7 @@
         <v>10</v>
       </c>
       <c r="D626">
-        <v>0.0009415309292910273</v>
+        <v>0.0009415309292910272</v>
       </c>
     </row>
     <row r="627">
@@ -11767,7 +11767,7 @@
         <v>10</v>
       </c>
       <c r="D634">
-        <v>0.0009415309292910273</v>
+        <v>0.0009415309292910272</v>
       </c>
     </row>
     <row r="635">
@@ -11929,7 +11929,7 @@
         <v>10</v>
       </c>
       <c r="D643">
-        <v>0.0009415309292910273</v>
+        <v>0.0009415309292910272</v>
       </c>
     </row>
     <row r="644">
@@ -11965,7 +11965,7 @@
         <v>10</v>
       </c>
       <c r="D645">
-        <v>0.0009415309292910273</v>
+        <v>0.0009415309292910272</v>
       </c>
     </row>
     <row r="646">
@@ -12091,7 +12091,7 @@
         <v>10</v>
       </c>
       <c r="D652">
-        <v>0.0009415309292910273</v>
+        <v>0.0009415309292910272</v>
       </c>
     </row>
     <row r="653">
@@ -13002,7 +13002,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec -Distrito 08-</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C703">
@@ -13560,7 +13560,7 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C734">
@@ -15439,7 +15439,7 @@
         <v>10</v>
       </c>
       <c r="D838">
-        <v>0.0009415309292910273</v>
+        <v>0.0009415309292910272</v>
       </c>
     </row>
     <row r="839">
@@ -16231,7 +16231,7 @@
         <v>10</v>
       </c>
       <c r="D882">
-        <v>0.0009415309292910273</v>
+        <v>0.0009415309292910272</v>
       </c>
     </row>
     <row r="883">
@@ -16879,7 +16879,7 @@
         <v>10</v>
       </c>
       <c r="D918">
-        <v>0.0009415309292910273</v>
+        <v>0.0009415309292910272</v>
       </c>
     </row>
     <row r="919">
@@ -17059,7 +17059,7 @@
         <v>10</v>
       </c>
       <c r="D928">
-        <v>0.0009415309292910273</v>
+        <v>0.0009415309292910272</v>
       </c>
     </row>
     <row r="929">
@@ -17869,7 +17869,7 @@
         <v>10</v>
       </c>
       <c r="D973">
-        <v>0.0009415309292910273</v>
+        <v>0.0009415309292910272</v>
       </c>
     </row>
     <row r="974">
@@ -19417,7 +19417,7 @@
         <v>10</v>
       </c>
       <c r="D1059">
-        <v>0.0009415309292910273</v>
+        <v>0.0009415309292910272</v>
       </c>
     </row>
     <row r="1060">
